--- a/R/inst/extdata/logistic_threshold_results.xlsx
+++ b/R/inst/extdata/logistic_threshold_results.xlsx
@@ -24,7 +24,7 @@
     <t xml:space="preserve">Cutoff</t>
   </si>
   <si>
-    <t xml:space="preserve">SBP</t>
+    <t xml:space="preserve">SOFA_CRRT_0h</t>
   </si>
   <si>
     <t xml:space="preserve">OR</t>
@@ -414,7 +414,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -456,22 +456,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>11.6332510235351</v>
+        <v>0.0418643866148393</v>
       </c>
       <c r="C2" t="n">
-        <v>0.725720062168756</v>
+        <v>0.45554017074771</v>
       </c>
       <c r="D2" t="n">
-        <v>3.38128652230066</v>
+        <v>-6.96605915067202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000721472692108503</v>
+        <v>0.00000000000325942147058982</v>
       </c>
       <c r="F2" t="n">
-        <v>2.85036808149063</v>
+        <v>0.0169365090385668</v>
       </c>
       <c r="G2" t="n">
-        <v>49.2740262106445</v>
+        <v>0.101167367666413</v>
       </c>
     </row>
     <row r="3">
@@ -479,22 +479,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.974056936654102</v>
+        <v>1.26696584409457</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00475138321017907</v>
+        <v>0.0209065997704178</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.53218281112052</v>
+        <v>11.3181935599198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000000316270020910167</v>
+        <v>0.0000000000000000000000000000106646837917503</v>
       </c>
       <c r="F3" t="n">
-        <v>0.964828934331848</v>
+        <v>1.21700499336771</v>
       </c>
       <c r="G3" t="n">
-        <v>0.982998773310113</v>
+        <v>1.32102445466801</v>
       </c>
     </row>
     <row r="4">
@@ -502,22 +502,22 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1.01036458092315</v>
+        <v>1.01277834844389</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00664170008427145</v>
+        <v>0.00454780478572942</v>
       </c>
       <c r="D4" t="n">
-        <v>1.55249963095868</v>
+        <v>2.79198313444803</v>
       </c>
       <c r="E4" t="n">
-        <v>0.120542720944579</v>
+        <v>0.00523860865480845</v>
       </c>
       <c r="F4" t="n">
-        <v>0.997334721303853</v>
+        <v>1.00380855878665</v>
       </c>
       <c r="G4" t="n">
-        <v>1.02369804832472</v>
+        <v>1.02188098133187</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +525,22 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>1.14781056016311</v>
+        <v>1.04995630252898</v>
       </c>
       <c r="C5" t="n">
-        <v>0.198077596378521</v>
+        <v>0.134719906265063</v>
       </c>
       <c r="D5" t="n">
-        <v>0.695971021061697</v>
+        <v>0.361851102898301</v>
       </c>
       <c r="E5" t="n">
-        <v>0.486446978105098</v>
+        <v>0.717463301485843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.779053169043136</v>
+        <v>0.806838137622801</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69491600596034</v>
+        <v>1.36853413635939</v>
       </c>
     </row>
   </sheetData>
@@ -582,22 +582,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>0.318532081293923</v>
+        <v>0.502004844714524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.530753726031472</v>
+        <v>0.366293289520557</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.15548573045169</v>
+        <v>-1.88140358621709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0311238440797464</v>
+        <v>0.0599170394063772</v>
       </c>
       <c r="F2" t="n">
-        <v>0.111148437472215</v>
+        <v>0.244170809540423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.894371057875401</v>
+        <v>1.02779557943859</v>
       </c>
     </row>
     <row r="3">
@@ -605,22 +605,22 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>1.03329876681083</v>
+        <v>0.743081230777148</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00672302535723063</v>
+        <v>0.056121587311911</v>
       </c>
       <c r="D3" t="n">
-        <v>4.87226643505955</v>
+        <v>-5.29118876291631</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00000110325246879572</v>
+        <v>0.000000121523858111162</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01999101203067</v>
+        <v>0.663131988898303</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0472671131141</v>
+        <v>0.826703052849224</v>
       </c>
     </row>
     <row r="4">
@@ -628,22 +628,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>0.993673227859228</v>
+        <v>1.23290102126743</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0147569287497311</v>
+        <v>0.0307729897210156</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.430094302817329</v>
+        <v>6.80369207333651</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667127044147406</v>
+        <v>0.0000000000101971378401634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.964259488508567</v>
+        <v>1.16188992053009</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0224806541189</v>
+        <v>1.31097760021324</v>
       </c>
     </row>
     <row r="5">
@@ -651,22 +651,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.01040000072017</v>
+        <v>1.01253354218059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00665870343968348</v>
+        <v>0.0045574756978013</v>
       </c>
       <c r="D5" t="n">
-        <v>1.55379990423447</v>
+        <v>2.7330145798549</v>
       </c>
       <c r="E5" t="n">
-        <v>0.120232153410105</v>
+        <v>0.00627575542068938</v>
       </c>
       <c r="F5" t="n">
-        <v>0.997341856235966</v>
+        <v>1.00354289035087</v>
       </c>
       <c r="G5" t="n">
-        <v>1.02377406942928</v>
+        <v>1.0216498484517</v>
       </c>
     </row>
     <row r="6">
@@ -674,22 +674,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1.12330383910071</v>
+        <v>1.04644369003285</v>
       </c>
       <c r="C6" t="n">
-        <v>0.198931586299283</v>
+        <v>0.134968442054981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.584493400575948</v>
+        <v>0.336356061203683</v>
       </c>
       <c r="E6" t="n">
-        <v>0.558888404009957</v>
+        <v>0.736602379217796</v>
       </c>
       <c r="F6" t="n">
-        <v>0.760983735158875</v>
+        <v>0.803757871816889</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66119160782433</v>
+        <v>1.36464478960162</v>
       </c>
     </row>
   </sheetData>
@@ -731,22 +731,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>23.2673825826967</v>
+        <v>0.0257674134503085</v>
       </c>
       <c r="C2" t="n">
-        <v>0.887986358371824</v>
+        <v>0.622952655455204</v>
       </c>
       <c r="D2" t="n">
-        <v>3.54403247413292</v>
+        <v>-5.87307012481689</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000394056705752408</v>
+        <v>0.00000000427797401155544</v>
       </c>
       <c r="F2" t="n">
-        <v>4.17369090566992</v>
+        <v>0.00735635587907842</v>
       </c>
       <c r="G2" t="n">
-        <v>136.394444734459</v>
+        <v>0.0849105089932563</v>
       </c>
     </row>
     <row r="3">
@@ -754,22 +754,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>1.02676132095988</v>
+        <v>0.916145608309806</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0187892187862021</v>
+        <v>0.0745523855336884</v>
       </c>
       <c r="D3" t="n">
-        <v>1.40556667673391</v>
+        <v>-1.17474397736733</v>
       </c>
       <c r="E3" t="n">
-        <v>0.159852837019963</v>
+        <v>0.240097159397993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.988849211695085</v>
+        <v>0.789558959615988</v>
       </c>
       <c r="G3" t="n">
-        <v>1.06510891210282</v>
+        <v>1.05804427256902</v>
       </c>
     </row>
     <row r="4">
@@ -777,22 +777,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.967774308960413</v>
+        <v>1.34574789213038</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00672302535723064</v>
+        <v>0.0561215873119112</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.87226643505955</v>
+        <v>5.29118876291626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00000110325246879571</v>
+        <v>0.000000121523858111196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.954866229902374</v>
+        <v>1.20962417708936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.980400795894392</v>
+        <v>1.5079954168119</v>
       </c>
     </row>
     <row r="5">
@@ -800,22 +800,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.01040000072017</v>
+        <v>1.01253354218059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00665870343968348</v>
+        <v>0.0045574756978013</v>
       </c>
       <c r="D5" t="n">
-        <v>1.55379990423446</v>
+        <v>2.7330145798549</v>
       </c>
       <c r="E5" t="n">
-        <v>0.120232153410106</v>
+        <v>0.00627575542068939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.997341856235966</v>
+        <v>1.00354289035087</v>
       </c>
       <c r="G5" t="n">
-        <v>1.02377406942928</v>
+        <v>1.0216498484517</v>
       </c>
     </row>
     <row r="6">
@@ -823,22 +823,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1.12330383910071</v>
+        <v>1.04644369003285</v>
       </c>
       <c r="C6" t="n">
-        <v>0.198931586299283</v>
+        <v>0.13496844205498</v>
       </c>
       <c r="D6" t="n">
-        <v>0.584493400575947</v>
+        <v>0.336356061203677</v>
       </c>
       <c r="E6" t="n">
-        <v>0.558888404009958</v>
+        <v>0.7366023792178</v>
       </c>
       <c r="F6" t="n">
-        <v>0.760983735158875</v>
+        <v>0.803757871816888</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66119160782433</v>
+        <v>1.36464478960162</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>-307.530461273969</v>
+        <v>-679.594635891442</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -885,16 +885,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>-306.569026751358</v>
+        <v>-678.891836095971</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.92286904522155</v>
+        <v>1.40559959094253</v>
       </c>
       <c r="E3" t="n">
-        <v>0.165540723287813</v>
+        <v>0.235788261932815</v>
       </c>
     </row>
   </sheetData>
